--- a/artfynd/A 40529-2026 artfynd.xlsx
+++ b/artfynd/A 40529-2026 artfynd.xlsx
@@ -2363,7 +2363,7 @@
         <v>137373471</v>
       </c>
       <c r="B17" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137373487</v>
       </c>
       <c r="B18" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137373499</v>
       </c>
       <c r="B19" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>137373508</v>
       </c>
       <c r="B20" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>137373515</v>
       </c>
       <c r="B21" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>137373516</v>
       </c>
       <c r="B22" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>137373517</v>
       </c>
       <c r="B23" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>137373520</v>
       </c>
       <c r="B24" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>137373548</v>
       </c>
       <c r="B25" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 40529-2026 artfynd.xlsx
+++ b/artfynd/A 40529-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137373477</v>
       </c>
       <c r="B2" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137373460</v>
       </c>
       <c r="B3" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137373467</v>
       </c>
       <c r="B4" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137373473</v>
       </c>
       <c r="B5" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137373475</v>
       </c>
       <c r="B6" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137373480</v>
       </c>
       <c r="B7" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137373484</v>
       </c>
       <c r="B8" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137373488</v>
       </c>
       <c r="B9" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137373498</v>
       </c>
       <c r="B10" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137373507</v>
       </c>
       <c r="B11" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137373530</v>
       </c>
       <c r="B12" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137373536</v>
       </c>
       <c r="B13" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137373538</v>
       </c>
       <c r="B14" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137373547</v>
       </c>
       <c r="B15" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137373506</v>
       </c>
       <c r="B16" t="n">
-        <v>81485</v>
+        <v>81490</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137373471</v>
       </c>
       <c r="B17" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137373487</v>
       </c>
       <c r="B18" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137373499</v>
       </c>
       <c r="B19" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>137373508</v>
       </c>
       <c r="B20" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>137373515</v>
       </c>
       <c r="B21" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>137373516</v>
       </c>
       <c r="B22" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>137373517</v>
       </c>
       <c r="B23" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>137373520</v>
       </c>
       <c r="B24" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>137373548</v>
       </c>
       <c r="B25" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>137373458</v>
       </c>
       <c r="B26" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>137373459</v>
       </c>
       <c r="B27" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>137373464</v>
       </c>
       <c r="B28" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>137373466</v>
       </c>
       <c r="B29" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>137373468</v>
       </c>
       <c r="B30" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>137373472</v>
       </c>
       <c r="B31" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>137373474</v>
       </c>
       <c r="B32" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>137373478</v>
       </c>
       <c r="B33" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>137373485</v>
       </c>
       <c r="B34" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>137373486</v>
       </c>
       <c r="B35" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>137373490</v>
       </c>
       <c r="B36" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>137373492</v>
       </c>
       <c r="B37" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>137373493</v>
       </c>
       <c r="B38" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>137373495</v>
       </c>
       <c r="B39" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>137373496</v>
       </c>
       <c r="B40" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>137373497</v>
       </c>
       <c r="B41" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>137373500</v>
       </c>
       <c r="B42" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5275,7 +5275,7 @@
         <v>137373519</v>
       </c>
       <c r="B43" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>137373534</v>
       </c>
       <c r="B44" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         <v>137373537</v>
       </c>
       <c r="B45" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>137373539</v>
       </c>
       <c r="B46" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         <v>137373541</v>
       </c>
       <c r="B47" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         <v>137373545</v>
       </c>
       <c r="B48" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
         <v>137373512</v>
       </c>
       <c r="B49" t="n">
-        <v>79540</v>
+        <v>79545</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6059,7 +6059,7 @@
         <v>137373514</v>
       </c>
       <c r="B50" t="n">
-        <v>79540</v>
+        <v>79545</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6171,7 +6171,7 @@
         <v>137373462</v>
       </c>
       <c r="B51" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>137373463</v>
       </c>
       <c r="B52" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>137373465</v>
       </c>
       <c r="B53" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         <v>137373479</v>
       </c>
       <c r="B54" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         <v>137373481</v>
       </c>
       <c r="B55" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>137373482</v>
       </c>
       <c r="B56" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6843,7 +6843,7 @@
         <v>137373489</v>
       </c>
       <c r="B57" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>137373494</v>
       </c>
       <c r="B58" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7067,7 +7067,7 @@
         <v>137373501</v>
       </c>
       <c r="B59" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7179,7 +7179,7 @@
         <v>137373503</v>
       </c>
       <c r="B60" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7291,7 +7291,7 @@
         <v>137373518</v>
       </c>
       <c r="B61" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>137373521</v>
       </c>
       <c r="B62" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         <v>137373522</v>
       </c>
       <c r="B63" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         <v>137373523</v>
       </c>
       <c r="B64" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7739,7 +7739,7 @@
         <v>137373526</v>
       </c>
       <c r="B65" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7851,7 +7851,7 @@
         <v>137373527</v>
       </c>
       <c r="B66" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7963,7 +7963,7 @@
         <v>137373529</v>
       </c>
       <c r="B67" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
         <v>137373532</v>
       </c>
       <c r="B68" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8187,7 +8187,7 @@
         <v>137373535</v>
       </c>
       <c r="B69" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8299,7 +8299,7 @@
         <v>137373542</v>
       </c>
       <c r="B70" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>137373502</v>
       </c>
       <c r="B78" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>137373505</v>
       </c>
       <c r="B79" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>137373511</v>
       </c>
       <c r="B80" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>137373531</v>
       </c>
       <c r="B81" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 40529-2026 artfynd.xlsx
+++ b/artfynd/A 40529-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137373477</v>
       </c>
       <c r="B2" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137373460</v>
       </c>
       <c r="B3" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137373467</v>
       </c>
       <c r="B4" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137373473</v>
       </c>
       <c r="B5" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137373475</v>
       </c>
       <c r="B6" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137373480</v>
       </c>
       <c r="B7" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137373484</v>
       </c>
       <c r="B8" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137373488</v>
       </c>
       <c r="B9" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137373498</v>
       </c>
       <c r="B10" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137373507</v>
       </c>
       <c r="B11" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137373530</v>
       </c>
       <c r="B12" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137373536</v>
       </c>
       <c r="B13" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137373538</v>
       </c>
       <c r="B14" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137373547</v>
       </c>
       <c r="B15" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137373506</v>
       </c>
       <c r="B16" t="n">
-        <v>81490</v>
+        <v>81501</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137373471</v>
       </c>
       <c r="B17" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137373487</v>
       </c>
       <c r="B18" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137373499</v>
       </c>
       <c r="B19" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>137373508</v>
       </c>
       <c r="B20" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>137373515</v>
       </c>
       <c r="B21" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>137373516</v>
       </c>
       <c r="B22" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>137373517</v>
       </c>
       <c r="B23" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>137373520</v>
       </c>
       <c r="B24" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>137373548</v>
       </c>
       <c r="B25" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>137373458</v>
       </c>
       <c r="B26" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>137373459</v>
       </c>
       <c r="B27" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>137373464</v>
       </c>
       <c r="B28" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>137373466</v>
       </c>
       <c r="B29" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>137373468</v>
       </c>
       <c r="B30" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>137373472</v>
       </c>
       <c r="B31" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>137373474</v>
       </c>
       <c r="B32" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>137373478</v>
       </c>
       <c r="B33" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>137373485</v>
       </c>
       <c r="B34" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>137373486</v>
       </c>
       <c r="B35" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>137373490</v>
       </c>
       <c r="B36" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>137373492</v>
       </c>
       <c r="B37" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>137373493</v>
       </c>
       <c r="B38" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>137373495</v>
       </c>
       <c r="B39" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>137373496</v>
       </c>
       <c r="B40" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>137373497</v>
       </c>
       <c r="B41" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>137373500</v>
       </c>
       <c r="B42" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5275,7 +5275,7 @@
         <v>137373519</v>
       </c>
       <c r="B43" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>137373534</v>
       </c>
       <c r="B44" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         <v>137373537</v>
       </c>
       <c r="B45" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>137373539</v>
       </c>
       <c r="B46" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         <v>137373541</v>
       </c>
       <c r="B47" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         <v>137373545</v>
       </c>
       <c r="B48" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
         <v>137373512</v>
       </c>
       <c r="B49" t="n">
-        <v>79545</v>
+        <v>79556</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6059,7 +6059,7 @@
         <v>137373514</v>
       </c>
       <c r="B50" t="n">
-        <v>79545</v>
+        <v>79556</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6171,7 +6171,7 @@
         <v>137373462</v>
       </c>
       <c r="B51" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>137373463</v>
       </c>
       <c r="B52" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>137373465</v>
       </c>
       <c r="B53" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         <v>137373479</v>
       </c>
       <c r="B54" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         <v>137373481</v>
       </c>
       <c r="B55" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>137373482</v>
       </c>
       <c r="B56" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6843,7 +6843,7 @@
         <v>137373489</v>
       </c>
       <c r="B57" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>137373494</v>
       </c>
       <c r="B58" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7067,7 +7067,7 @@
         <v>137373501</v>
       </c>
       <c r="B59" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7179,7 +7179,7 @@
         <v>137373503</v>
       </c>
       <c r="B60" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7291,7 +7291,7 @@
         <v>137373518</v>
       </c>
       <c r="B61" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>137373521</v>
       </c>
       <c r="B62" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         <v>137373522</v>
       </c>
       <c r="B63" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         <v>137373523</v>
       </c>
       <c r="B64" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7739,7 +7739,7 @@
         <v>137373526</v>
       </c>
       <c r="B65" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7851,7 +7851,7 @@
         <v>137373527</v>
       </c>
       <c r="B66" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7963,7 +7963,7 @@
         <v>137373529</v>
       </c>
       <c r="B67" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
         <v>137373532</v>
       </c>
       <c r="B68" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8187,7 +8187,7 @@
         <v>137373535</v>
       </c>
       <c r="B69" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8299,7 +8299,7 @@
         <v>137373542</v>
       </c>
       <c r="B70" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>137373502</v>
       </c>
       <c r="B78" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>137373505</v>
       </c>
       <c r="B79" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>137373511</v>
       </c>
       <c r="B80" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>137373531</v>
       </c>
       <c r="B81" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 40529-2026 artfynd.xlsx
+++ b/artfynd/A 40529-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137373477</v>
       </c>
       <c r="B2" t="n">
-        <v>79564</v>
+        <v>79565</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137373460</v>
       </c>
       <c r="B3" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137373467</v>
       </c>
       <c r="B4" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137373473</v>
       </c>
       <c r="B5" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137373475</v>
       </c>
       <c r="B6" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137373480</v>
       </c>
       <c r="B7" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137373484</v>
       </c>
       <c r="B8" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137373488</v>
       </c>
       <c r="B9" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137373498</v>
       </c>
       <c r="B10" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137373507</v>
       </c>
       <c r="B11" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137373530</v>
       </c>
       <c r="B12" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137373536</v>
       </c>
       <c r="B13" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137373538</v>
       </c>
       <c r="B14" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137373547</v>
       </c>
       <c r="B15" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137373506</v>
       </c>
       <c r="B16" t="n">
-        <v>81501</v>
+        <v>81502</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137373471</v>
       </c>
       <c r="B17" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137373487</v>
       </c>
       <c r="B18" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137373499</v>
       </c>
       <c r="B19" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>137373508</v>
       </c>
       <c r="B20" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>137373515</v>
       </c>
       <c r="B21" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>137373516</v>
       </c>
       <c r="B22" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>137373517</v>
       </c>
       <c r="B23" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>137373520</v>
       </c>
       <c r="B24" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>137373548</v>
       </c>
       <c r="B25" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>137373458</v>
       </c>
       <c r="B26" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>137373459</v>
       </c>
       <c r="B27" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>137373464</v>
       </c>
       <c r="B28" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>137373466</v>
       </c>
       <c r="B29" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>137373468</v>
       </c>
       <c r="B30" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>137373472</v>
       </c>
       <c r="B31" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>137373474</v>
       </c>
       <c r="B32" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>137373478</v>
       </c>
       <c r="B33" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>137373485</v>
       </c>
       <c r="B34" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>137373486</v>
       </c>
       <c r="B35" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>137373490</v>
       </c>
       <c r="B36" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>137373492</v>
       </c>
       <c r="B37" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>137373493</v>
       </c>
       <c r="B38" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>137373495</v>
       </c>
       <c r="B39" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>137373496</v>
       </c>
       <c r="B40" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>137373497</v>
       </c>
       <c r="B41" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>137373500</v>
       </c>
       <c r="B42" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5275,7 +5275,7 @@
         <v>137373519</v>
       </c>
       <c r="B43" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>137373534</v>
       </c>
       <c r="B44" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         <v>137373537</v>
       </c>
       <c r="B45" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>137373539</v>
       </c>
       <c r="B46" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         <v>137373541</v>
       </c>
       <c r="B47" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         <v>137373545</v>
       </c>
       <c r="B48" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
         <v>137373512</v>
       </c>
       <c r="B49" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6059,7 +6059,7 @@
         <v>137373514</v>
       </c>
       <c r="B50" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6171,7 +6171,7 @@
         <v>137373462</v>
       </c>
       <c r="B51" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>137373463</v>
       </c>
       <c r="B52" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>137373465</v>
       </c>
       <c r="B53" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         <v>137373479</v>
       </c>
       <c r="B54" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         <v>137373481</v>
       </c>
       <c r="B55" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>137373482</v>
       </c>
       <c r="B56" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6843,7 +6843,7 @@
         <v>137373489</v>
       </c>
       <c r="B57" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>137373494</v>
       </c>
       <c r="B58" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7067,7 +7067,7 @@
         <v>137373501</v>
       </c>
       <c r="B59" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7179,7 +7179,7 @@
         <v>137373503</v>
       </c>
       <c r="B60" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7291,7 +7291,7 @@
         <v>137373518</v>
       </c>
       <c r="B61" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>137373521</v>
       </c>
       <c r="B62" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         <v>137373522</v>
       </c>
       <c r="B63" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         <v>137373523</v>
       </c>
       <c r="B64" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7739,7 +7739,7 @@
         <v>137373526</v>
       </c>
       <c r="B65" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7851,7 +7851,7 @@
         <v>137373527</v>
       </c>
       <c r="B66" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7963,7 +7963,7 @@
         <v>137373529</v>
       </c>
       <c r="B67" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
         <v>137373532</v>
       </c>
       <c r="B68" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8187,7 +8187,7 @@
         <v>137373535</v>
       </c>
       <c r="B69" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8299,7 +8299,7 @@
         <v>137373542</v>
       </c>
       <c r="B70" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>137373502</v>
       </c>
       <c r="B78" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>137373505</v>
       </c>
       <c r="B79" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>137373511</v>
       </c>
       <c r="B80" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>137373531</v>
       </c>
       <c r="B81" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 40529-2026 artfynd.xlsx
+++ b/artfynd/A 40529-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137373477</v>
       </c>
       <c r="B2" t="n">
-        <v>79565</v>
+        <v>79567</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137373460</v>
       </c>
       <c r="B3" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137373467</v>
       </c>
       <c r="B4" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137373473</v>
       </c>
       <c r="B5" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137373475</v>
       </c>
       <c r="B6" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137373480</v>
       </c>
       <c r="B7" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137373484</v>
       </c>
       <c r="B8" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137373488</v>
       </c>
       <c r="B9" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137373498</v>
       </c>
       <c r="B10" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137373507</v>
       </c>
       <c r="B11" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137373530</v>
       </c>
       <c r="B12" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137373536</v>
       </c>
       <c r="B13" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137373538</v>
       </c>
       <c r="B14" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137373547</v>
       </c>
       <c r="B15" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137373506</v>
       </c>
       <c r="B16" t="n">
-        <v>81502</v>
+        <v>81504</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137373471</v>
       </c>
       <c r="B17" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137373487</v>
       </c>
       <c r="B18" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137373499</v>
       </c>
       <c r="B19" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>137373508</v>
       </c>
       <c r="B20" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>137373515</v>
       </c>
       <c r="B21" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>137373516</v>
       </c>
       <c r="B22" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>137373517</v>
       </c>
       <c r="B23" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>137373520</v>
       </c>
       <c r="B24" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>137373548</v>
       </c>
       <c r="B25" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>137373458</v>
       </c>
       <c r="B26" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>137373459</v>
       </c>
       <c r="B27" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>137373464</v>
       </c>
       <c r="B28" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>137373466</v>
       </c>
       <c r="B29" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>137373468</v>
       </c>
       <c r="B30" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>137373472</v>
       </c>
       <c r="B31" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>137373474</v>
       </c>
       <c r="B32" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>137373478</v>
       </c>
       <c r="B33" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>137373485</v>
       </c>
       <c r="B34" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>137373486</v>
       </c>
       <c r="B35" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>137373490</v>
       </c>
       <c r="B36" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>137373492</v>
       </c>
       <c r="B37" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>137373493</v>
       </c>
       <c r="B38" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>137373495</v>
       </c>
       <c r="B39" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>137373496</v>
       </c>
       <c r="B40" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>137373497</v>
       </c>
       <c r="B41" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>137373500</v>
       </c>
       <c r="B42" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5275,7 +5275,7 @@
         <v>137373519</v>
       </c>
       <c r="B43" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>137373534</v>
       </c>
       <c r="B44" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         <v>137373537</v>
       </c>
       <c r="B45" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>137373539</v>
       </c>
       <c r="B46" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         <v>137373541</v>
       </c>
       <c r="B47" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         <v>137373545</v>
       </c>
       <c r="B48" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
         <v>137373512</v>
       </c>
       <c r="B49" t="n">
-        <v>79557</v>
+        <v>79559</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6059,7 +6059,7 @@
         <v>137373514</v>
       </c>
       <c r="B50" t="n">
-        <v>79557</v>
+        <v>79559</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6171,7 +6171,7 @@
         <v>137373462</v>
       </c>
       <c r="B51" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>137373463</v>
       </c>
       <c r="B52" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>137373465</v>
       </c>
       <c r="B53" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         <v>137373479</v>
       </c>
       <c r="B54" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         <v>137373481</v>
       </c>
       <c r="B55" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>137373482</v>
       </c>
       <c r="B56" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6843,7 +6843,7 @@
         <v>137373489</v>
       </c>
       <c r="B57" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>137373494</v>
       </c>
       <c r="B58" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7067,7 +7067,7 @@
         <v>137373501</v>
       </c>
       <c r="B59" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7179,7 +7179,7 @@
         <v>137373503</v>
       </c>
       <c r="B60" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7291,7 +7291,7 @@
         <v>137373518</v>
       </c>
       <c r="B61" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>137373521</v>
       </c>
       <c r="B62" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         <v>137373522</v>
       </c>
       <c r="B63" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         <v>137373523</v>
       </c>
       <c r="B64" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7739,7 +7739,7 @@
         <v>137373526</v>
       </c>
       <c r="B65" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7851,7 +7851,7 @@
         <v>137373527</v>
       </c>
       <c r="B66" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7963,7 +7963,7 @@
         <v>137373529</v>
       </c>
       <c r="B67" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
         <v>137373532</v>
       </c>
       <c r="B68" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8187,7 +8187,7 @@
         <v>137373535</v>
       </c>
       <c r="B69" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8299,7 +8299,7 @@
         <v>137373542</v>
       </c>
       <c r="B70" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>137373502</v>
       </c>
       <c r="B78" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>137373505</v>
       </c>
       <c r="B79" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>137373511</v>
       </c>
       <c r="B80" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>137373531</v>
       </c>
       <c r="B81" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 40529-2026 artfynd.xlsx
+++ b/artfynd/A 40529-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137373477</v>
       </c>
       <c r="B2" t="n">
-        <v>79567</v>
+        <v>79571</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137373460</v>
       </c>
       <c r="B3" t="n">
-        <v>79201</v>
+        <v>79205</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137373467</v>
       </c>
       <c r="B4" t="n">
-        <v>79201</v>
+        <v>79205</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137373473</v>
       </c>
       <c r="B5" t="n">
-        <v>79201</v>
+        <v>79205</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137373475</v>
       </c>
       <c r="B6" t="n">
-        <v>79201</v>
+        <v>79205</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137373480</v>
       </c>
       <c r="B7" t="n">
-        <v>79201</v>
+        <v>79205</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137373484</v>
       </c>
       <c r="B8" t="n">
-        <v>79201</v>
+        <v>79205</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137373488</v>
       </c>
       <c r="B9" t="n">
-        <v>79201</v>
+        <v>79205</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137373498</v>
       </c>
       <c r="B10" t="n">
-        <v>79201</v>
+        <v>79205</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137373507</v>
       </c>
       <c r="B11" t="n">
-        <v>79201</v>
+        <v>79205</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137373530</v>
       </c>
       <c r="B12" t="n">
-        <v>79201</v>
+        <v>79205</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137373536</v>
       </c>
       <c r="B13" t="n">
-        <v>79201</v>
+        <v>79205</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137373538</v>
       </c>
       <c r="B14" t="n">
-        <v>79201</v>
+        <v>79205</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137373547</v>
       </c>
       <c r="B15" t="n">
-        <v>79201</v>
+        <v>79205</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137373506</v>
       </c>
       <c r="B16" t="n">
-        <v>81504</v>
+        <v>81508</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137373471</v>
       </c>
       <c r="B17" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137373487</v>
       </c>
       <c r="B18" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137373499</v>
       </c>
       <c r="B19" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>137373508</v>
       </c>
       <c r="B20" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>137373515</v>
       </c>
       <c r="B21" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>137373516</v>
       </c>
       <c r="B22" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>137373517</v>
       </c>
       <c r="B23" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>137373520</v>
       </c>
       <c r="B24" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>137373548</v>
       </c>
       <c r="B25" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>137373458</v>
       </c>
       <c r="B26" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>137373459</v>
       </c>
       <c r="B27" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>137373464</v>
       </c>
       <c r="B28" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>137373466</v>
       </c>
       <c r="B29" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>137373468</v>
       </c>
       <c r="B30" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>137373472</v>
       </c>
       <c r="B31" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>137373474</v>
       </c>
       <c r="B32" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>137373478</v>
       </c>
       <c r="B33" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>137373485</v>
       </c>
       <c r="B34" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>137373486</v>
       </c>
       <c r="B35" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>137373490</v>
       </c>
       <c r="B36" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>137373492</v>
       </c>
       <c r="B37" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>137373493</v>
       </c>
       <c r="B38" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>137373495</v>
       </c>
       <c r="B39" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>137373496</v>
       </c>
       <c r="B40" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>137373497</v>
       </c>
       <c r="B41" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>137373500</v>
       </c>
       <c r="B42" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5275,7 +5275,7 @@
         <v>137373519</v>
       </c>
       <c r="B43" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>137373534</v>
       </c>
       <c r="B44" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         <v>137373537</v>
       </c>
       <c r="B45" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>137373539</v>
       </c>
       <c r="B46" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         <v>137373541</v>
       </c>
       <c r="B47" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         <v>137373545</v>
       </c>
       <c r="B48" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
         <v>137373512</v>
       </c>
       <c r="B49" t="n">
-        <v>79559</v>
+        <v>79563</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6059,7 +6059,7 @@
         <v>137373514</v>
       </c>
       <c r="B50" t="n">
-        <v>79559</v>
+        <v>79563</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6171,7 +6171,7 @@
         <v>137373462</v>
       </c>
       <c r="B51" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>137373463</v>
       </c>
       <c r="B52" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>137373465</v>
       </c>
       <c r="B53" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         <v>137373479</v>
       </c>
       <c r="B54" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         <v>137373481</v>
       </c>
       <c r="B55" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>137373482</v>
       </c>
       <c r="B56" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6843,7 +6843,7 @@
         <v>137373489</v>
       </c>
       <c r="B57" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>137373494</v>
       </c>
       <c r="B58" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7067,7 +7067,7 @@
         <v>137373501</v>
       </c>
       <c r="B59" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7179,7 +7179,7 @@
         <v>137373503</v>
       </c>
       <c r="B60" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7291,7 +7291,7 @@
         <v>137373518</v>
       </c>
       <c r="B61" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>137373521</v>
       </c>
       <c r="B62" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         <v>137373522</v>
       </c>
       <c r="B63" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         <v>137373523</v>
       </c>
       <c r="B64" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7739,7 +7739,7 @@
         <v>137373526</v>
       </c>
       <c r="B65" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7851,7 +7851,7 @@
         <v>137373527</v>
       </c>
       <c r="B66" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7963,7 +7963,7 @@
         <v>137373529</v>
       </c>
       <c r="B67" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
         <v>137373532</v>
       </c>
       <c r="B68" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8187,7 +8187,7 @@
         <v>137373535</v>
       </c>
       <c r="B69" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8299,7 +8299,7 @@
         <v>137373542</v>
       </c>
       <c r="B70" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>137373502</v>
       </c>
       <c r="B78" t="n">
-        <v>80125</v>
+        <v>80129</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>137373505</v>
       </c>
       <c r="B79" t="n">
-        <v>80125</v>
+        <v>80129</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>137373511</v>
       </c>
       <c r="B80" t="n">
-        <v>80125</v>
+        <v>80129</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>137373531</v>
       </c>
       <c r="B81" t="n">
-        <v>80125</v>
+        <v>80129</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
